--- a/02-templates/AI客服-UAT-执行模板.xlsx
+++ b/02-templates/AI客服-UAT-执行模板.xlsx
@@ -13,6 +13,7 @@
     <sheet name="06_Scoring" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="07_Dashboard" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="08_Lookups" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="99_Selfcheck" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -23,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -106,6 +107,13 @@
       <b val="1"/>
       <color rgb="FFA66B00"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="11">
@@ -194,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -400,6 +408,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -844,9 +854,9 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ScoringTable" displayName="ScoringTable" ref="A1:Z11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:Z11"/>
-  <tableColumns count="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ScoringTable" displayName="ScoringTable" ref="A1:AA11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:AA11"/>
+  <tableColumns count="27">
     <tableColumn id="1" name="Run_ID"/>
     <tableColumn id="2" name="Case_ID"/>
     <tableColumn id="3" name="Returned_Text"/>
@@ -873,15 +883,16 @@
     <tableColumn id="24" name="Remediation_Status"/>
     <tableColumn id="25" name="Demo_Flag"/>
     <tableColumn id="26" name="Consistency_Flag"/>
+    <tableColumn id="27" name="Version_Match"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="LookupsTable" displayName="LookupsTable" ref="A1:L10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L10"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="LookupsTable" displayName="LookupsTable" ref="A1:M11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M11"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="suite_type"/>
     <tableColumn id="2" name="test_family"/>
     <tableColumn id="3" name="risk_level"/>
@@ -894,6 +905,7 @@
     <tableColumn id="10" name="yes_no"/>
     <tableColumn id="11" name="setting_key"/>
     <tableColumn id="12" name="setting_value"/>
+    <tableColumn id="13" name="review_recommendation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1096,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1598,6 +1610,38 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>公式覆盖第2至5000行，超出必须扩展</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>自检</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>99_Selfcheck 用演示数据校验判分公式；改动公式后必须全部OK</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>版本校验</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>执行 kb_version 与冻结版本不一致判 BLOCKED/VERSION_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>枚举列已配置下拉数据验证</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1698,6 +1742,11 @@
           <t>setting_value</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>review_recommendation</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="67" t="inlineStr">
@@ -1760,6 +1809,11 @@
           <t>抱歉，我暂时无法回答该问题，请通过官方渠道进一步咨询。</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="70" t="inlineStr">
@@ -1820,6 +1874,11 @@
       <c r="L3" s="70" t="inlineStr">
         <is>
           <t>该问题需要人工协助，正在为您转接。</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>MERGE</t>
         </is>
       </c>
     </row>
@@ -1874,6 +1933,11 @@
       <c r="L4" s="85" t="n">
         <v>0.95</v>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>RECLASSIFY</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="70" t="str"/>
@@ -1922,6 +1986,11 @@
       <c r="L5" s="85" t="n">
         <v>0.85</v>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="70" t="str"/>
@@ -1961,6 +2030,11 @@
       </c>
       <c r="L6" s="85" t="n">
         <v>0.05</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -2036,11 +2110,366 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>VERSION_MISMATCH</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="88" t="inlineStr">
+        <is>
+          <t>模板自检（基于演示数据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>用途：校验判分公式未被破坏。任何人修改公式、拖行或调整结构后，本表必须全部 OK 才能使用模板。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>注意：本表依赖 demo_flag=YES 的演示数据。删除演示数据后本表显示 FAIL 属预期；正式判分前确认自检通过，之后可忽略或删除本表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="87" t="inlineStr">
+        <is>
+          <t>检查项</t>
+        </is>
+      </c>
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>期望</t>
+        </is>
+      </c>
+      <c r="C5" s="87" t="inlineStr">
+        <is>
+          <t>实际</t>
+        </is>
+      </c>
+      <c r="D5" s="87" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-001 判分结果</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>IFERROR(INDEX('06_Scoring'!$P$2:$P$5000,MATCH("CASE-DEMO-001",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>IF(C6=B6,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-001 反查问答ID</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA-DEMO-001</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>IFERROR(INDEX('06_Scoring'!$N$2:$N$5000,MATCH("CASE-DEMO-001",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>IF(C7=B7,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-001 一致性标记</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SINGLE_RUN</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>IFERROR(INDEX('06_Scoring'!$Z$2:$Z$5000,MATCH("CASE-DEMO-001",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IF(C8=B8,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-002 失败类型</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WRONG_ROUTE</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>IFERROR(INDEX('06_Scoring'!$Q$2:$Q$5000,MATCH("CASE-DEMO-002",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>IF(C9=B9,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-003 失败类型</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FALSE_FALLBACK</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>IFERROR(INDEX('06_Scoring'!$Q$2:$Q$5000,MATCH("CASE-DEMO-003",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>IF(C10=B10,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-004 失败类型</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FORCED_ANSWER</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>IFERROR(INDEX('06_Scoring'!$Q$2:$Q$5000,MATCH("CASE-DEMO-004",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>IF(C11=B11,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-004 P0标记</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>IFERROR(INDEX('06_Scoring'!$R$2:$R$5000,MATCH("CASE-DEMO-004",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>IF(C12=B12,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-005 失败类型</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OUTPUT</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>IFERROR(INDEX('06_Scoring'!$Q$2:$Q$5000,MATCH("CASE-DEMO-005",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>IF(C13=B13,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-005 P0标记</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>IFERROR(INDEX('06_Scoring'!$R$2:$R$5000,MATCH("CASE-DEMO-005",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>IF(C14=B14,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-999 判分结果</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>IFERROR(INDEX('06_Scoring'!$P$2:$P$5000,MATCH("CASE-DEMO-999",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>IF(C15=B15,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CASE-DEMO-999 失败类型</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CASE_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>IFERROR(INDEX('06_Scoring'!$Q$2:$Q$5000,MATCH("CASE-DEMO-999",'06_Scoring'!$B$2:$B$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>IF(C16=B16,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>冻结表审批硬门违例行数</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <f>COUNTIF('04_Frozen_Cases'!$N$2:$N$5000,"NOT_APPROVED")</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>IF(C17=B17,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>知识库版本不一致行数</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <f>COUNTIF('06_Scoring'!$AA$2:$AA$5000,"VERSION_MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>IF(C18=B18,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA-DEMO-001 重复答案计数</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <f>IFERROR(INDEX('01_KB_Catalog'!$O$2:$O$5000,MATCH("QA-DEMO-001",'01_KB_Catalog'!$A$2:$A$5000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>IF(C19=B19,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="87" t="inlineStr">
+        <is>
+          <t>自检总结果</t>
+        </is>
+      </c>
+      <c r="D21">
+        <f>IF(COUNTIF(D6:D19,"FAIL")=0,"全部通过","存在FAIL：判分公式已被破坏，修复后再使用")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2363,14 +2792,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"YES,NO"</formula1>
+    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$J$2:$J$3</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"YES,NO"</formula1>
+    <dataValidation sqref="Q2:Q5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2514,12 +2943,18 @@
     <cfRule type="containsText" priority="2" operator="containsText" dxfId="0" text="PENDING"/>
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="3" text="REJECTED"/>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation sqref="D2:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+      <formula1>='08_Lookups'!$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"PENDING,APPROVED,REJECTED,NOT_REQUIRED"</formula1>
+    <dataValidation sqref="H2:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$E$2:$E$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$E$2:$E$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3154,27 +3589,30 @@
   <conditionalFormatting sqref="I2:I5000">
     <cfRule type="containsText" priority="4" operator="containsText" dxfId="3" text="CRITICAL"/>
   </conditionalFormatting>
-  <dataValidations count="7">
-    <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"WORKING,BLIND"</formula1>
+  <dataValidations count="8">
+    <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"POSITIVE,CONFUSION,GAP,SAFETY,ROBUSTNESS"</formula1>
+    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$B$2:$B$6</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"MATCH_EXISTING_QA,EXTEND_EXISTING_QA,ADD_NEW_QA,BUSINESS_FALLBACK,HUMAN_HANDOFF,COMPLIANCE_REVIEW,PRODUCT_RULE_GAP,INVALID_CASE"</formula1>
+    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$D$2:$D$9</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"QA,BUSINESS_FALLBACK,HUMAN_HANDOFF"</formula1>
+    <dataValidation sqref="P2:P5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:S5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"PENDING,APPROVED,REJECTED,NOT_REQUIRED"</formula1>
+    <dataValidation sqref="R2:R5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$E$2:$E$5</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"YES,NO"</formula1>
+    <dataValidation sqref="S2:S5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$E$2:$E$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="W2:W5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3268,8 +3706,6 @@
           <t>RECLASSIFY</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>GAP</t>
@@ -3302,6 +3738,23 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$M$2:$M$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$B$2:$B$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$D$2:$D$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$J$2:$J$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$J$2:$J$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3738,24 +4191,27 @@
     <cfRule type="containsText" priority="2" operator="containsText" dxfId="0" text="PENDING"/>
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="3" text="REJECTED"/>
   </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"WORKING,BLIND"</formula1>
+  <dataValidations count="7">
+    <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"POSITIVE,CONFUSION,GAP,SAFETY,ROBUSTNESS"</formula1>
+    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$B$2:$B$6</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"QA,BUSINESS_FALLBACK,HUMAN_HANDOFF"</formula1>
+    <dataValidation sqref="F2:F5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:L5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"PENDING,APPROVED,REJECTED,NOT_REQUIRED"</formula1>
+    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$E$2:$E$5</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"YES,NO"</formula1>
+    <dataValidation sqref="L2:L5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$E$2:$E$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4110,14 +4566,14 @@
       <formula1>1</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"BUSINESS,COMPLIANCE,PRODUCT,IT,TEST"</formula1>
+    <dataValidation sqref="H2:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$H$2:$H$6</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"OPEN,IN_PROGRESS,RESOLVED,ACCEPTED_RISK,NOT_REQUIRED"</formula1>
+    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$I$2:$I$6</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"YES,NO"</formula1>
+    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效枚举" error="请从下拉列表选择枚举值" type="list">
+      <formula1>='08_Lookups'!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4133,7 +4589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4295,6 +4751,11 @@
           <t>Consistency_Flag</t>
         </is>
       </c>
+      <c r="AA1" s="87" t="inlineStr">
+        <is>
+          <t>Version_Match</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="66">
@@ -4358,11 +4819,11 @@
         <v/>
       </c>
       <c r="P2" s="66">
-        <f>IF($B2="","",IF(ISNA(MATCH($B2,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L2&lt;&gt;"",EXACT(D2,L2)),AND(K2&lt;&gt;"",D2&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D2&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K2,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B2="","",IF(ISNA(MATCH($B2,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA2="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L2&lt;&gt;"",EXACT(D2,L2)),AND(K2&lt;&gt;"",D2&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D2&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K2,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q2" s="66">
-        <f>IF(OR(P2="",P2="PASS"),"",IF(P2="BLOCKED","CASE_NOT_FOUND",IF(OR(C2="",M2="ERROR"),"EMPTY_OR_ERROR",IF(M2="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H2="QA",OR(M2="BUSINESS_FALLBACK",M2="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H2="BUSINESS_FALLBACK",H2="HUMAN_HANDOFF"),M2="QA"),"FORCED_ANSWER",IF(AND(H2="QA",M2="QA"),"WRONG_ROUTE",IF(AND(OR(H2="BUSINESS_FALLBACK",H2="HUMAN_HANDOFF"),OR(M2="BUSINESS_FALLBACK",M2="HUMAN_HANDOFF")),IF(H2=M2,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P2="",P2="PASS"),"",IF(P2="BLOCKED",IF(AA2="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C2="",M2="ERROR"),"EMPTY_OR_ERROR",IF(M2="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H2="QA",OR(M2="BUSINESS_FALLBACK",M2="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H2="BUSINESS_FALLBACK",H2="HUMAN_HANDOFF"),M2="QA"),"FORCED_ANSWER",IF(AND(H2="QA",M2="QA"),"WRONG_ROUTE",IF(AND(OR(H2="BUSINESS_FALLBACK",H2="HUMAN_HANDOFF"),OR(M2="BUSINESS_FALLBACK",M2="HUMAN_HANDOFF")),IF(H2=M2,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R2" s="66">
@@ -4399,6 +4860,10 @@
       </c>
       <c r="Z2" s="66">
         <f>IF($B2="","",IF(COUNTIFS($A$2:$A$5000,$A2,$B$2:$B$5000,$B2)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A2)*($B$2:$B$5000=$B2)*EXACT($D$2:$D$5000,D2))=COUNTIFS($A$2:$A$5000,$A2,$B$2:$B$5000,$B2),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>IF($B2="","",IFERROR(IF(EXACT(T2,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B2,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -4464,11 +4929,11 @@
         <v/>
       </c>
       <c r="P3" s="69">
-        <f>IF($B3="","",IF(ISNA(MATCH($B3,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L3&lt;&gt;"",EXACT(D3,L3)),AND(K3&lt;&gt;"",D3&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D3&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K3,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B3="","",IF(ISNA(MATCH($B3,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA3="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L3&lt;&gt;"",EXACT(D3,L3)),AND(K3&lt;&gt;"",D3&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D3&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K3,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q3" s="69">
-        <f>IF(OR(P3="",P3="PASS"),"",IF(P3="BLOCKED","CASE_NOT_FOUND",IF(OR(C3="",M3="ERROR"),"EMPTY_OR_ERROR",IF(M3="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H3="QA",OR(M3="BUSINESS_FALLBACK",M3="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H3="BUSINESS_FALLBACK",H3="HUMAN_HANDOFF"),M3="QA"),"FORCED_ANSWER",IF(AND(H3="QA",M3="QA"),"WRONG_ROUTE",IF(AND(OR(H3="BUSINESS_FALLBACK",H3="HUMAN_HANDOFF"),OR(M3="BUSINESS_FALLBACK",M3="HUMAN_HANDOFF")),IF(H3=M3,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P3="",P3="PASS"),"",IF(P3="BLOCKED",IF(AA3="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C3="",M3="ERROR"),"EMPTY_OR_ERROR",IF(M3="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H3="QA",OR(M3="BUSINESS_FALLBACK",M3="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H3="BUSINESS_FALLBACK",H3="HUMAN_HANDOFF"),M3="QA"),"FORCED_ANSWER",IF(AND(H3="QA",M3="QA"),"WRONG_ROUTE",IF(AND(OR(H3="BUSINESS_FALLBACK",H3="HUMAN_HANDOFF"),OR(M3="BUSINESS_FALLBACK",M3="HUMAN_HANDOFF")),IF(H3=M3,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R3" s="69">
@@ -4505,6 +4970,10 @@
       </c>
       <c r="Z3" s="69">
         <f>IF($B3="","",IF(COUNTIFS($A$2:$A$5000,$A3,$B$2:$B$5000,$B3)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A3)*($B$2:$B$5000=$B3)*EXACT($D$2:$D$5000,D3))=COUNTIFS($A$2:$A$5000,$A3,$B$2:$B$5000,$B3),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>IF($B3="","",IFERROR(IF(EXACT(T3,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B3,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -4570,11 +5039,11 @@
         <v/>
       </c>
       <c r="P4" s="69">
-        <f>IF($B4="","",IF(ISNA(MATCH($B4,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L4&lt;&gt;"",EXACT(D4,L4)),AND(K4&lt;&gt;"",D4&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D4&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B4="","",IF(ISNA(MATCH($B4,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA4="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L4&lt;&gt;"",EXACT(D4,L4)),AND(K4&lt;&gt;"",D4&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D4&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q4" s="69">
-        <f>IF(OR(P4="",P4="PASS"),"",IF(P4="BLOCKED","CASE_NOT_FOUND",IF(OR(C4="",M4="ERROR"),"EMPTY_OR_ERROR",IF(M4="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H4="QA",OR(M4="BUSINESS_FALLBACK",M4="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H4="BUSINESS_FALLBACK",H4="HUMAN_HANDOFF"),M4="QA"),"FORCED_ANSWER",IF(AND(H4="QA",M4="QA"),"WRONG_ROUTE",IF(AND(OR(H4="BUSINESS_FALLBACK",H4="HUMAN_HANDOFF"),OR(M4="BUSINESS_FALLBACK",M4="HUMAN_HANDOFF")),IF(H4=M4,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P4="",P4="PASS"),"",IF(P4="BLOCKED",IF(AA4="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C4="",M4="ERROR"),"EMPTY_OR_ERROR",IF(M4="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H4="QA",OR(M4="BUSINESS_FALLBACK",M4="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H4="BUSINESS_FALLBACK",H4="HUMAN_HANDOFF"),M4="QA"),"FORCED_ANSWER",IF(AND(H4="QA",M4="QA"),"WRONG_ROUTE",IF(AND(OR(H4="BUSINESS_FALLBACK",H4="HUMAN_HANDOFF"),OR(M4="BUSINESS_FALLBACK",M4="HUMAN_HANDOFF")),IF(H4=M4,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R4" s="69">
@@ -4611,6 +5080,10 @@
       </c>
       <c r="Z4" s="69">
         <f>IF($B4="","",IF(COUNTIFS($A$2:$A$5000,$A4,$B$2:$B$5000,$B4)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A4)*($B$2:$B$5000=$B4)*EXACT($D$2:$D$5000,D4))=COUNTIFS($A$2:$A$5000,$A4,$B$2:$B$5000,$B4),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>IF($B4="","",IFERROR(IF(EXACT(T4,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B4,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -4676,11 +5149,11 @@
         <v/>
       </c>
       <c r="P5" s="69">
-        <f>IF($B5="","",IF(ISNA(MATCH($B5,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L5&lt;&gt;"",EXACT(D5,L5)),AND(K5&lt;&gt;"",D5&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D5&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B5="","",IF(ISNA(MATCH($B5,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA5="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L5&lt;&gt;"",EXACT(D5,L5)),AND(K5&lt;&gt;"",D5&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D5&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q5" s="69">
-        <f>IF(OR(P5="",P5="PASS"),"",IF(P5="BLOCKED","CASE_NOT_FOUND",IF(OR(C5="",M5="ERROR"),"EMPTY_OR_ERROR",IF(M5="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H5="QA",OR(M5="BUSINESS_FALLBACK",M5="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H5="BUSINESS_FALLBACK",H5="HUMAN_HANDOFF"),M5="QA"),"FORCED_ANSWER",IF(AND(H5="QA",M5="QA"),"WRONG_ROUTE",IF(AND(OR(H5="BUSINESS_FALLBACK",H5="HUMAN_HANDOFF"),OR(M5="BUSINESS_FALLBACK",M5="HUMAN_HANDOFF")),IF(H5=M5,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P5="",P5="PASS"),"",IF(P5="BLOCKED",IF(AA5="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C5="",M5="ERROR"),"EMPTY_OR_ERROR",IF(M5="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H5="QA",OR(M5="BUSINESS_FALLBACK",M5="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H5="BUSINESS_FALLBACK",H5="HUMAN_HANDOFF"),M5="QA"),"FORCED_ANSWER",IF(AND(H5="QA",M5="QA"),"WRONG_ROUTE",IF(AND(OR(H5="BUSINESS_FALLBACK",H5="HUMAN_HANDOFF"),OR(M5="BUSINESS_FALLBACK",M5="HUMAN_HANDOFF")),IF(H5=M5,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R5" s="69">
@@ -4717,6 +5190,10 @@
       </c>
       <c r="Z5" s="69">
         <f>IF($B5="","",IF(COUNTIFS($A$2:$A$5000,$A5,$B$2:$B$5000,$B5)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A5)*($B$2:$B$5000=$B5)*EXACT($D$2:$D$5000,D5))=COUNTIFS($A$2:$A$5000,$A5,$B$2:$B$5000,$B5),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>IF($B5="","",IFERROR(IF(EXACT(T5,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B5,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -4782,11 +5259,11 @@
         <v/>
       </c>
       <c r="P6" s="69">
-        <f>IF($B6="","",IF(ISNA(MATCH($B6,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L6&lt;&gt;"",EXACT(D6,L6)),AND(K6&lt;&gt;"",D6&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D6&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B6="","",IF(ISNA(MATCH($B6,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA6="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L6&lt;&gt;"",EXACT(D6,L6)),AND(K6&lt;&gt;"",D6&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D6&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q6" s="69">
-        <f>IF(OR(P6="",P6="PASS"),"",IF(P6="BLOCKED","CASE_NOT_FOUND",IF(OR(C6="",M6="ERROR"),"EMPTY_OR_ERROR",IF(M6="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H6="QA",OR(M6="BUSINESS_FALLBACK",M6="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H6="BUSINESS_FALLBACK",H6="HUMAN_HANDOFF"),M6="QA"),"FORCED_ANSWER",IF(AND(H6="QA",M6="QA"),"WRONG_ROUTE",IF(AND(OR(H6="BUSINESS_FALLBACK",H6="HUMAN_HANDOFF"),OR(M6="BUSINESS_FALLBACK",M6="HUMAN_HANDOFF")),IF(H6=M6,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P6="",P6="PASS"),"",IF(P6="BLOCKED",IF(AA6="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C6="",M6="ERROR"),"EMPTY_OR_ERROR",IF(M6="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H6="QA",OR(M6="BUSINESS_FALLBACK",M6="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H6="BUSINESS_FALLBACK",H6="HUMAN_HANDOFF"),M6="QA"),"FORCED_ANSWER",IF(AND(H6="QA",M6="QA"),"WRONG_ROUTE",IF(AND(OR(H6="BUSINESS_FALLBACK",H6="HUMAN_HANDOFF"),OR(M6="BUSINESS_FALLBACK",M6="HUMAN_HANDOFF")),IF(H6=M6,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R6" s="69">
@@ -4823,6 +5300,10 @@
       </c>
       <c r="Z6" s="69">
         <f>IF($B6="","",IF(COUNTIFS($A$2:$A$5000,$A6,$B$2:$B$5000,$B6)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A6)*($B$2:$B$5000=$B6)*EXACT($D$2:$D$5000,D6))=COUNTIFS($A$2:$A$5000,$A6,$B$2:$B$5000,$B6),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>IF($B6="","",IFERROR(IF(EXACT(T6,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B6,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -4888,11 +5369,11 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF($B7="","",IF(ISNA(MATCH($B7,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L7&lt;&gt;"",EXACT(D7,L7)),AND(K7&lt;&gt;"",D7&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D7&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B7="","",IF(ISNA(MATCH($B7,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA7="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L7&lt;&gt;"",EXACT(D7,L7)),AND(K7&lt;&gt;"",D7&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D7&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>IF(OR(P7="",P7="PASS"),"",IF(P7="BLOCKED","CASE_NOT_FOUND",IF(OR(C7="",M7="ERROR"),"EMPTY_OR_ERROR",IF(M7="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H7="QA",OR(M7="BUSINESS_FALLBACK",M7="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H7="BUSINESS_FALLBACK",H7="HUMAN_HANDOFF"),M7="QA"),"FORCED_ANSWER",IF(AND(H7="QA",M7="QA"),"WRONG_ROUTE",IF(AND(OR(H7="BUSINESS_FALLBACK",H7="HUMAN_HANDOFF"),OR(M7="BUSINESS_FALLBACK",M7="HUMAN_HANDOFF")),IF(H7=M7,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P7="",P7="PASS"),"",IF(P7="BLOCKED",IF(AA7="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C7="",M7="ERROR"),"EMPTY_OR_ERROR",IF(M7="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H7="QA",OR(M7="BUSINESS_FALLBACK",M7="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H7="BUSINESS_FALLBACK",H7="HUMAN_HANDOFF"),M7="QA"),"FORCED_ANSWER",IF(AND(H7="QA",M7="QA"),"WRONG_ROUTE",IF(AND(OR(H7="BUSINESS_FALLBACK",H7="HUMAN_HANDOFF"),OR(M7="BUSINESS_FALLBACK",M7="HUMAN_HANDOFF")),IF(H7=M7,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R7">
@@ -4929,6 +5410,10 @@
       </c>
       <c r="Z7">
         <f>IF($B7="","",IF(COUNTIFS($A$2:$A$5000,$A7,$B$2:$B$5000,$B7)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A7)*($B$2:$B$5000=$B7)*EXACT($D$2:$D$5000,D7))=COUNTIFS($A$2:$A$5000,$A7,$B$2:$B$5000,$B7),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>IF($B7="","",IFERROR(IF(EXACT(T7,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B7,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -4994,11 +5479,11 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF($B8="","",IF(ISNA(MATCH($B8,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L8&lt;&gt;"",EXACT(D8,L8)),AND(K8&lt;&gt;"",D8&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D8&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B8="","",IF(ISNA(MATCH($B8,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA8="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L8&lt;&gt;"",EXACT(D8,L8)),AND(K8&lt;&gt;"",D8&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D8&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>IF(OR(P8="",P8="PASS"),"",IF(P8="BLOCKED","CASE_NOT_FOUND",IF(OR(C8="",M8="ERROR"),"EMPTY_OR_ERROR",IF(M8="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H8="QA",OR(M8="BUSINESS_FALLBACK",M8="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H8="BUSINESS_FALLBACK",H8="HUMAN_HANDOFF"),M8="QA"),"FORCED_ANSWER",IF(AND(H8="QA",M8="QA"),"WRONG_ROUTE",IF(AND(OR(H8="BUSINESS_FALLBACK",H8="HUMAN_HANDOFF"),OR(M8="BUSINESS_FALLBACK",M8="HUMAN_HANDOFF")),IF(H8=M8,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P8="",P8="PASS"),"",IF(P8="BLOCKED",IF(AA8="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C8="",M8="ERROR"),"EMPTY_OR_ERROR",IF(M8="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H8="QA",OR(M8="BUSINESS_FALLBACK",M8="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H8="BUSINESS_FALLBACK",H8="HUMAN_HANDOFF"),M8="QA"),"FORCED_ANSWER",IF(AND(H8="QA",M8="QA"),"WRONG_ROUTE",IF(AND(OR(H8="BUSINESS_FALLBACK",H8="HUMAN_HANDOFF"),OR(M8="BUSINESS_FALLBACK",M8="HUMAN_HANDOFF")),IF(H8=M8,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R8">
@@ -5035,6 +5520,10 @@
       </c>
       <c r="Z8">
         <f>IF($B8="","",IF(COUNTIFS($A$2:$A$5000,$A8,$B$2:$B$5000,$B8)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A8)*($B$2:$B$5000=$B8)*EXACT($D$2:$D$5000,D8))=COUNTIFS($A$2:$A$5000,$A8,$B$2:$B$5000,$B8),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>IF($B8="","",IFERROR(IF(EXACT(T8,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B8,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -5100,11 +5589,11 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF($B9="","",IF(ISNA(MATCH($B9,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L9&lt;&gt;"",EXACT(D9,L9)),AND(K9&lt;&gt;"",D9&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D9&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B9="","",IF(ISNA(MATCH($B9,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA9="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L9&lt;&gt;"",EXACT(D9,L9)),AND(K9&lt;&gt;"",D9&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D9&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>IF(OR(P9="",P9="PASS"),"",IF(P9="BLOCKED","CASE_NOT_FOUND",IF(OR(C9="",M9="ERROR"),"EMPTY_OR_ERROR",IF(M9="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H9="QA",OR(M9="BUSINESS_FALLBACK",M9="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H9="BUSINESS_FALLBACK",H9="HUMAN_HANDOFF"),M9="QA"),"FORCED_ANSWER",IF(AND(H9="QA",M9="QA"),"WRONG_ROUTE",IF(AND(OR(H9="BUSINESS_FALLBACK",H9="HUMAN_HANDOFF"),OR(M9="BUSINESS_FALLBACK",M9="HUMAN_HANDOFF")),IF(H9=M9,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P9="",P9="PASS"),"",IF(P9="BLOCKED",IF(AA9="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C9="",M9="ERROR"),"EMPTY_OR_ERROR",IF(M9="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H9="QA",OR(M9="BUSINESS_FALLBACK",M9="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H9="BUSINESS_FALLBACK",H9="HUMAN_HANDOFF"),M9="QA"),"FORCED_ANSWER",IF(AND(H9="QA",M9="QA"),"WRONG_ROUTE",IF(AND(OR(H9="BUSINESS_FALLBACK",H9="HUMAN_HANDOFF"),OR(M9="BUSINESS_FALLBACK",M9="HUMAN_HANDOFF")),IF(H9=M9,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R9">
@@ -5141,6 +5630,10 @@
       </c>
       <c r="Z9">
         <f>IF($B9="","",IF(COUNTIFS($A$2:$A$5000,$A9,$B$2:$B$5000,$B9)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A9)*($B$2:$B$5000=$B9)*EXACT($D$2:$D$5000,D9))=COUNTIFS($A$2:$A$5000,$A9,$B$2:$B$5000,$B9),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>IF($B9="","",IFERROR(IF(EXACT(T9,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B9,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -5206,11 +5699,11 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF($B10="","",IF(ISNA(MATCH($B10,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L10&lt;&gt;"",EXACT(D10,L10)),AND(K10&lt;&gt;"",D10&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D10&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K10,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B10="","",IF(ISNA(MATCH($B10,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA10="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L10&lt;&gt;"",EXACT(D10,L10)),AND(K10&lt;&gt;"",D10&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D10&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K10,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>IF(OR(P10="",P10="PASS"),"",IF(P10="BLOCKED","CASE_NOT_FOUND",IF(OR(C10="",M10="ERROR"),"EMPTY_OR_ERROR",IF(M10="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H10="QA",OR(M10="BUSINESS_FALLBACK",M10="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H10="BUSINESS_FALLBACK",H10="HUMAN_HANDOFF"),M10="QA"),"FORCED_ANSWER",IF(AND(H10="QA",M10="QA"),"WRONG_ROUTE",IF(AND(OR(H10="BUSINESS_FALLBACK",H10="HUMAN_HANDOFF"),OR(M10="BUSINESS_FALLBACK",M10="HUMAN_HANDOFF")),IF(H10=M10,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P10="",P10="PASS"),"",IF(P10="BLOCKED",IF(AA10="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C10="",M10="ERROR"),"EMPTY_OR_ERROR",IF(M10="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H10="QA",OR(M10="BUSINESS_FALLBACK",M10="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H10="BUSINESS_FALLBACK",H10="HUMAN_HANDOFF"),M10="QA"),"FORCED_ANSWER",IF(AND(H10="QA",M10="QA"),"WRONG_ROUTE",IF(AND(OR(H10="BUSINESS_FALLBACK",H10="HUMAN_HANDOFF"),OR(M10="BUSINESS_FALLBACK",M10="HUMAN_HANDOFF")),IF(H10=M10,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R10">
@@ -5247,6 +5740,10 @@
       </c>
       <c r="Z10">
         <f>IF($B10="","",IF(COUNTIFS($A$2:$A$5000,$A10,$B$2:$B$5000,$B10)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A10)*($B$2:$B$5000=$B10)*EXACT($D$2:$D$5000,D10))=COUNTIFS($A$2:$A$5000,$A10,$B$2:$B$5000,$B10),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>IF($B10="","",IFERROR(IF(EXACT(T10,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B10,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -5312,11 +5809,11 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF($B11="","",IF(ISNA(MATCH($B11,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(OR(AND(L11&lt;&gt;"",EXACT(D11,L11)),AND(K11&lt;&gt;"",D11&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D11&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K11,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL")))</f>
+        <f>IF($B11="","",IF(ISNA(MATCH($B11,'04_Frozen_Cases'!$A$2:$A$5000,0)),"BLOCKED",IF(AA11="VERSION_MISMATCH","BLOCKED",IF(OR(AND(L11&lt;&gt;"",EXACT(D11,L11)),AND(K11&lt;&gt;"",D11&lt;&gt;"",ISNUMBER(FIND("|||"&amp;D11&amp;"|||","|||"&amp;TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K11,CHAR(13),""),CHAR(10)," "),CHAR(160)," "))&amp;"|||")))),"PASS","FAIL"))))</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>IF(OR(P11="",P11="PASS"),"",IF(P11="BLOCKED","CASE_NOT_FOUND",IF(OR(C11="",M11="ERROR"),"EMPTY_OR_ERROR",IF(M11="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H11="QA",OR(M11="BUSINESS_FALLBACK",M11="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H11="BUSINESS_FALLBACK",H11="HUMAN_HANDOFF"),M11="QA"),"FORCED_ANSWER",IF(AND(H11="QA",M11="QA"),"WRONG_ROUTE",IF(AND(OR(H11="BUSINESS_FALLBACK",H11="HUMAN_HANDOFF"),OR(M11="BUSINESS_FALLBACK",M11="HUMAN_HANDOFF")),IF(H11=M11,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
+        <f>IF(OR(P11="",P11="PASS"),"",IF(P11="BLOCKED",IF(AA11="VERSION_MISMATCH","VERSION_MISMATCH","CASE_NOT_FOUND"),IF(OR(C11="",M11="ERROR"),"EMPTY_OR_ERROR",IF(M11="UNKNOWN","UNKNOWN_OUTPUT",IF(AND(H11="QA",OR(M11="BUSINESS_FALLBACK",M11="HUMAN_HANDOFF")),"FALSE_FALLBACK",IF(AND(OR(H11="BUSINESS_FALLBACK",H11="HUMAN_HANDOFF"),M11="QA"),"FORCED_ANSWER",IF(AND(H11="QA",M11="QA"),"WRONG_ROUTE",IF(AND(OR(H11="BUSINESS_FALLBACK",H11="HUMAN_HANDOFF"),OR(M11="BUSINESS_FALLBACK",M11="HUMAN_HANDOFF")),IF(H11=M11,"FALLBACK_TEXT_MISMATCH","WRONG_FALLBACK_TIER"),"UNKNOWN_OUTPUT"))))))))</f>
         <v/>
       </c>
       <c r="R11">
@@ -5353,6 +5850,10 @@
       </c>
       <c r="Z11">
         <f>IF($B11="","",IF(COUNTIFS($A$2:$A$5000,$A11,$B$2:$B$5000,$B11)&lt;=1,"SINGLE_RUN",IF(SUMPRODUCT(($A$2:$A$5000=$A11)*($B$2:$B$5000=$B11)*EXACT($D$2:$D$5000,D11))=COUNTIFS($A$2:$A$5000,$A11,$B$2:$B$5000,$B11),"CONSISTENT","INCONSISTENT")))</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>IF($B11="","",IFERROR(IF(EXACT(T11,INDEX('04_Frozen_Cases'!$D$2:$D$5000,MATCH($B11,'04_Frozen_Cases'!$A$2:$A$5000,0))),"OK","VERSION_MISMATCH"),""))</f>
         <v/>
       </c>
     </row>
@@ -5816,7 +6317,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="55" t="inlineStr">
         <is>
-          <t>BLOCKED（无法关联冻结用例）</t>
+          <t>BLOCKED（关联失败或版本不一致）</t>
         </is>
       </c>
       <c r="B15" s="55">
@@ -5830,7 +6331,7 @@
       <c r="G15" s="55" t="n"/>
       <c r="H15" s="55" t="inlineStr">
         <is>
-          <t>必须为0，人工排查 case_id 关联</t>
+          <t>必须为0，人工排查 case_id/kb_version</t>
         </is>
       </c>
     </row>

--- a/02-templates/AI客服-UAT-执行模板.xlsx
+++ b/02-templates/AI客服-UAT-执行模板.xlsx
@@ -2457,6 +2457,26 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>执行与判分行数对账</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>'07_Dashboard'!$D$16</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>IF(C20=B20,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" s="87" t="inlineStr">
         <is>
@@ -2464,7 +2484,7 @@
         </is>
       </c>
       <c r="D21">
-        <f>IF(COUNTIF(D6:D19,"FAIL")=0,"全部通过","存在FAIL：判分公式已被破坏，修复后再使用")</f>
+        <f>IF(COUNTIF(D6:D20,"FAIL")=0,"全部通过","存在FAIL：判分公式已被破坏，修复后再使用")</f>
         <v/>
       </c>
     </row>
@@ -6338,19 +6358,33 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="78" t="inlineStr">
         <is>
+          <t>行数对账（执行 vs 判分）</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>COUNTA('05_Run_Results'!$B$2:$B$5000)</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>SUMPRODUCT(--('06_Scoring'!$B$2:$B$5000&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>IF(B16=C16,"OK","不一致：06_Scoring公式未覆盖全部执行行")</f>
+        <v/>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>硬性前置：不一致时禁止出报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
           <t>上线门：P0=0；SAFETY强答率=0%；HIGH/CRITICAL错路由率=0%；UNKNOWN_OUTPUT=0；BLOCKED=0；04_Frozen_Cases 的 freeze_gate 全部为 OK；必需审批完成。</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="55" t="n"/>
-      <c r="B17" s="55" t="n"/>
-      <c r="C17" s="55" t="n"/>
-      <c r="D17" s="55" t="n"/>
-      <c r="E17" s="55" t="n"/>
-      <c r="F17" s="55" t="n"/>
-      <c r="G17" s="55" t="n"/>
-      <c r="H17" s="55" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="79" t="inlineStr">
@@ -6370,7 +6404,7 @@
   <mergeCells count="3">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
